--- a/data/trans_dic/P43B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P43B-Habitat-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,2</t>
+          <t>4,92; 11,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,94</t>
+          <t>5,75; 12,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,65</t>
+          <t>7,22; 12,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,2</t>
+          <t>4,92; 11,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,94</t>
+          <t>5,75; 12,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,65</t>
+          <t>7,22; 12,58</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 15,25</t>
+          <t>8,66; 14,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,21</t>
+          <t>8,32; 13,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,23</t>
+          <t>11,84; 17,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 15,25</t>
+          <t>8,66; 14,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,21</t>
+          <t>8,32; 13,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,23</t>
+          <t>11,84; 17,4</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 24,44</t>
+          <t>15,54; 24,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,34</t>
+          <t>7,42; 14,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 23,35</t>
+          <t>19,92; 28,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 24,44</t>
+          <t>15,54; 24,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,34</t>
+          <t>7,42; 14,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 23,35</t>
+          <t>19,92; 28,31</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 21,07</t>
+          <t>13,67; 21,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,12</t>
+          <t>14,25; 21,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,25</t>
+          <t>20,64; 27,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 21,07</t>
+          <t>13,67; 21,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,12</t>
+          <t>14,25; 21,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,25</t>
+          <t>20,64; 27,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,25</t>
+          <t>12,4; 16,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,88; 14,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,56</t>
+          <t>16,88; 20,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,25</t>
+          <t>12,4; 16,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,88; 14,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,56</t>
+          <t>16,88; 20,34</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27967</t>
         </is>
       </c>
     </row>
@@ -1180,32 +1180,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15517; 36511</t>
+          <t>16050; 38568</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18261; 38627</t>
+          <t>18604; 39381</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19519; 34306</t>
+          <t>20873; 36395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15517; 36511</t>
+          <t>16050; 38568</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18261; 38627</t>
+          <t>18604; 39381</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19519; 34306</t>
+          <t>20873; 36395</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>57892</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1298,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39779; 69270</t>
+          <t>39360; 67268</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42617; 71905</t>
+          <t>42091; 70458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40429; 62422</t>
+          <t>47517; 69801</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39779; 69270</t>
+          <t>39360; 67268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42617; 71905</t>
+          <t>42091; 70458</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40429; 62422</t>
+          <t>47517; 69801</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63626</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63626</t>
+          <t>71347</t>
         </is>
       </c>
     </row>
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55280; 87725</t>
+          <t>55774; 88383</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24590; 48287</t>
+          <t>24999; 48076</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23370; 117817</t>
+          <t>59165; 84064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55280; 87725</t>
+          <t>55774; 88383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24590; 48287</t>
+          <t>24999; 48076</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23370; 117817</t>
+          <t>59165; 84064</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105316</t>
+          <t>113118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>105316</t>
+          <t>113118</t>
         </is>
       </c>
     </row>
@@ -1534,32 +1534,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69704; 104554</t>
+          <t>67845; 104663</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73316; 110866</t>
+          <t>74772; 111623</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90036; 120976</t>
+          <t>98673; 129267</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69704; 104554</t>
+          <t>67845; 104663</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73316; 110866</t>
+          <t>74772; 111623</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90036; 120976</t>
+          <t>98673; 129267</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>270325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>270325</t>
         </is>
       </c>
     </row>
@@ -1652,32 +1652,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>202807; 265865</t>
+          <t>202798; 263179</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>180886; 238679</t>
+          <t>183949; 238421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161854; 293714</t>
+          <t>247339; 297997</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202807; 265865</t>
+          <t>202798; 263179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>180886; 238679</t>
+          <t>183949; 238421</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>161854; 293714</t>
+          <t>247339; 297997</t>
         </is>
       </c>
     </row>
